--- a/Question Bank/ai-ml-genai-agenticai-questions-bank.xlsx
+++ b/Question Bank/ai-ml-genai-agenticai-questions-bank.xlsx
@@ -1,23 +1,170 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Ai Tools" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+  <si>
+    <t>Coding Assisant</t>
+  </si>
+  <si>
+    <t>Github Copilot</t>
+  </si>
+  <si>
+    <t>Cursor</t>
+  </si>
+  <si>
+    <t>Devin</t>
+  </si>
+  <si>
+    <t>Claude AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes Assistant </t>
+  </si>
+  <si>
+    <t>Chat GPT</t>
+  </si>
+  <si>
+    <t>Deepseek</t>
+  </si>
+  <si>
+    <t>Prompt Assisant</t>
+  </si>
+  <si>
+    <t>Anthropic</t>
+  </si>
+  <si>
+    <t>https://anthropic.skilljar.com/ asbhosale.1987@gmail.com/ Jesus@1987</t>
+  </si>
+  <si>
+    <t>Codex</t>
+  </si>
+  <si>
+    <t>Local LLM</t>
+  </si>
+  <si>
+    <r>
+      <t>Local text LLMs (Ollama)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → Perfect for coding help, training material, quizzes, etc.</t>
+    </r>
+  </si>
+  <si>
+    <t>new Oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">? </t>
+  </si>
+  <si>
+    <t>existing system motor</t>
+  </si>
+  <si>
+    <t>reliable source</t>
+  </si>
+  <si>
+    <t>on earth</t>
+  </si>
+  <si>
+    <t>POC</t>
+  </si>
+  <si>
+    <t>existing oil</t>
+  </si>
+  <si>
+    <t>20-30 yr</t>
+  </si>
+  <si>
+    <t>300 yr</t>
+  </si>
+  <si>
+    <t>Analysis new oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask prayer element </t>
+  </si>
+  <si>
+    <t>New oil+ element= Existing oil</t>
+  </si>
+  <si>
+    <t>5000 per/month</t>
+  </si>
+  <si>
+    <t>all Country</t>
+  </si>
+  <si>
+    <t>1 LacsLitre</t>
+  </si>
+  <si>
+    <t>10k litre</t>
+  </si>
+  <si>
+    <t>1yr</t>
+  </si>
+  <si>
+    <t>300yr</t>
+  </si>
+  <si>
+    <t>72 lacs litre</t>
+  </si>
+  <si>
+    <t>Per country</t>
+  </si>
+  <si>
+    <t>250 countries</t>
+  </si>
+  <si>
+    <t>100 yrs</t>
+  </si>
+  <si>
+    <t>1800 millions</t>
+  </si>
+  <si>
+    <t>18 billion</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Litre</t>
+  </si>
+  <si>
+    <t>3500 gallion</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>4litre</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -25,13 +172,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,14 +220,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -343,28 +529,247 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="E8:T20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="8" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="Q8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" s="5"/>
+      <c r="S8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="Q9" t="s">
+        <v>30</v>
+      </c>
+      <c r="R9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="O10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10">
+        <f>250*72</f>
+        <v>18000</v>
+      </c>
+      <c r="T10">
+        <f>100*72</f>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="11" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11">
+        <v>250</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>48000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="R16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="R17" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="Q8:R8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>